--- a/grupos/1DV - Estadisticos 20211.xlsx
+++ b/grupos/1DV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="134">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,229 +197,229 @@
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZALAVA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CARLOS URIEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MARIN</t>
   </si>
   <si>
-    <t>MONT</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>MOSTRANZO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZALAVA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>GARNICA</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CARLOS URIEL</t>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
   </si>
   <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
-    <t>NATALIE</t>
+    <t>GAEL</t>
   </si>
   <si>
     <t>CRISTIAN FERMIN</t>
   </si>
   <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
     <t>IKER XAVIER</t>
   </si>
   <si>
-    <t>THANIA CRISTAL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>DANIEL OCTAVIO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
   </si>
   <si>
     <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
   </si>
 </sst>
 </file>
@@ -914,13 +914,13 @@
         <v>-1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>-1</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -932,7 +932,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -968,13 +968,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>-1</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1000,22 +1000,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1039,13 +1039,13 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1077,22 +1077,22 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1119,10 +1119,10 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1154,22 +1154,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1193,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1205,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1231,22 +1231,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1267,7 +1267,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1282,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1299,7 +1299,7 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1308,22 +1308,22 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1344,22 +1344,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1385,22 +1385,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1421,7 +1421,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1453,16 +1453,16 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1471,10 +1471,10 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1507,13 +1507,13 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1539,7 +1539,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1548,10 +1548,10 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1616,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1625,10 +1625,10 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1661,10 +1661,10 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1684,16 +1684,16 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1702,10 +1702,10 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1738,13 +1738,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1752,7 +1752,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1770,22 +1770,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1806,10 +1806,10 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1821,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1838,13 +1838,13 @@
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1856,13 +1856,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1892,13 +1892,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1924,19 +1924,19 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1966,10 +1966,10 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2001,22 +2001,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2037,7 +2037,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2046,13 +2046,13 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2078,22 +2078,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2123,13 +2123,13 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2143,7 +2143,7 @@
         <v>8</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>9</v>
@@ -2155,22 +2155,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2197,16 +2197,16 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2232,19 +2232,19 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2277,10 +2277,10 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2300,13 +2300,13 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2315,16 +2315,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2354,13 +2354,13 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2368,16 +2368,16 @@
         <v>31</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2386,7 +2386,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2406,13 +2406,13 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>-1</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2460,13 +2460,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>-1</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2492,22 +2492,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2531,7 +2531,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2569,22 +2569,22 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2605,7 +2605,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2617,10 +2617,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2646,22 +2646,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2682,7 +2682,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2691,13 +2691,13 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2723,22 +2723,22 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2759,13 +2759,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2791,13 +2791,13 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>-1</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2845,13 +2845,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2859,7 +2859,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -2868,16 +2868,16 @@
         <v>6</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>7</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2886,10 +2886,10 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2913,7 +2913,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2922,13 +2922,13 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2945,13 +2945,13 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -2963,10 +2963,10 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -2999,13 +2999,13 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3070,57 +3070,57 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>64.29000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>35.71</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>28</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>64.29000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G3">
-        <v>32.14</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3.57</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3128,100 +3128,100 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>29</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>79.31</v>
+      </c>
+      <c r="G4">
+        <v>20.69</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>68.97</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.7</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>31.03</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>71.43000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>28.57</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>75.86</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>24.14</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3230,25 +3230,25 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3258,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3293,16 +3293,16 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3313,16 +3313,16 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3333,33 +3333,33 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920110</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>51</v>
@@ -3367,39 +3367,39 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920110</v>
+        <v>21330051920391</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>49</v>
@@ -3407,19 +3407,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920117</v>
+        <v>21330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
@@ -3427,119 +3427,119 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920117</v>
+        <v>21330051920127</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920120</v>
+        <v>21330051920128</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920120</v>
+        <v>21330051920128</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920120</v>
+        <v>21330051920128</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920121</v>
+        <v>20330051920152</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920391</v>
+        <v>20330051920152</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
@@ -3547,19 +3547,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920391</v>
+        <v>20330051920152</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>52</v>
@@ -3567,542 +3567,22 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920391</v>
+        <v>21330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920391</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920391</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920122</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920127</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920127</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920127</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920127</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920275</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920128</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920128</v>
-      </c>
-      <c r="B27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920128</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920128</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920152</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920152</v>
-      </c>
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920152</v>
-      </c>
-      <c r="B33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920152</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920152</v>
-      </c>
-      <c r="B35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920133</v>
-      </c>
-      <c r="B36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920133</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920133</v>
-      </c>
-      <c r="B38" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920134</v>
-      </c>
-      <c r="B39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920134</v>
-      </c>
-      <c r="B40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920134</v>
-      </c>
-      <c r="B41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920134</v>
-      </c>
-      <c r="B42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4144,245 +3624,245 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920391</v>
+        <v>21330051920128</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920128</v>
+        <v>20330051920152</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920152</v>
+        <v>21330051920391</v>
       </c>
       <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920127</v>
+        <v>21330051920120</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920134</v>
+        <v>21330051920122</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920120</v>
+        <v>21330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920133</v>
+        <v>21330051920134</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920117</v>
+        <v>21330051920111</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920115</v>
+        <v>21330051920112</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920121</v>
+        <v>21330051920113</v>
       </c>
       <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920122</v>
+        <v>21330051920114</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920126</v>
+        <v>21330051920115</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920275</v>
+        <v>21330051920116</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920111</v>
+        <v>21330051920117</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>120</v>
@@ -4393,16 +3873,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920112</v>
+        <v>21330051920118</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4410,16 +3890,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920113</v>
+        <v>21330051920119</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4427,16 +3907,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920114</v>
+        <v>21330051920121</v>
       </c>
       <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
         <v>99</v>
       </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4444,16 +3924,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920116</v>
+        <v>21330051920123</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4461,16 +3941,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920118</v>
+        <v>21330051920124</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4478,13 +3958,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920119</v>
+        <v>21330051920125</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>125</v>
@@ -4495,13 +3975,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920123</v>
+        <v>21330051920126</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>126</v>
@@ -4512,13 +3992,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920124</v>
+        <v>20330051920275</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
         <v>127</v>
@@ -4529,13 +4009,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920125</v>
-      </c>
-      <c r="B25" t="s">
-        <v>103</v>
+        <v>21330051920129</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
         <v>128</v>
@@ -4546,10 +4023,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920129</v>
+        <v>21330051920130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>129</v>
@@ -4560,13 +4040,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920130</v>
+        <v>21330051920131</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
         <v>130</v>
@@ -4577,13 +4057,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920131</v>
+        <v>18330051920377</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>131</v>
@@ -4594,13 +4074,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>18330051920377</v>
+        <v>21330051920132</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
         <v>132</v>
@@ -4611,13 +4091,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920132</v>
+        <v>21330051920133</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
         <v>133</v>
@@ -4633,7 +4113,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4665,22 +4145,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920121</v>
+        <v>21330051920120</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4688,19 +4168,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920121</v>
+        <v>21330051920120</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
@@ -4711,19 +4191,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920115</v>
+        <v>21330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
@@ -4734,22 +4214,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920118</v>
+        <v>21330051920127</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4757,71 +4237,94 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920122</v>
+        <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920126</v>
+        <v>21330051920118</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920275</v>
+        <v>21330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
         <v>92</v>
       </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
+      <c r="D9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1DV - Estadisticos 20211.xlsx
+++ b/grupos/1DV - Estadisticos 20211.xlsx
@@ -1619,7 +1619,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1655,7 +1655,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>

--- a/grupos/1DV - Estadisticos 20211.xlsx
+++ b/grupos/1DV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="134">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,6 +197,30 @@
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -206,34 +230,109 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>MONT</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>MOSTRANZO</t>
   </si>
   <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>ZALAVA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>CAPORAL</t>
   </si>
   <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
@@ -242,184 +341,85 @@
     <t>CARLOS URIEL</t>
   </si>
   <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
     <t>NATALIE</t>
   </si>
   <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
     <t>LOGAN FRANCISCO</t>
   </si>
   <si>
     <t>CLAUDIA</t>
   </si>
   <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
     <t>PAUL ADRIAN</t>
   </si>
   <si>
+    <t>IKER XAVIER</t>
+  </si>
+  <si>
     <t>THANIA CRISTAL</t>
   </si>
   <si>
+    <t>DANIEL OCTAVIO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
     <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IKER XAVIER</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -905,73 +905,73 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1018,22 +1018,22 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1048,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1095,31 +1095,31 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1128,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1172,37 +1172,37 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1249,31 +1249,31 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1282,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1326,22 +1326,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1350,10 +1350,10 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1403,22 +1403,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1465,10 +1465,10 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1477,31 +1477,31 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>6</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1510,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1542,10 +1542,10 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -1554,40 +1554,40 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>7</v>
@@ -1631,43 +1631,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1696,10 +1696,10 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1708,34 +1708,34 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1788,31 +1788,31 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>7</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1829,13 +1829,13 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1847,13 +1847,13 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -1865,40 +1865,40 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1909,7 +1909,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1927,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -1939,31 +1939,31 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1972,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -2019,25 +2019,25 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2096,22 +2096,22 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2120,16 +2120,16 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2173,22 +2173,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2200,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2235,7 +2235,7 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2247,31 +2247,31 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2280,10 +2280,10 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2291,7 +2291,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2309,10 +2309,10 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2327,40 +2327,40 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2380,13 +2380,13 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2397,73 +2397,73 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2510,22 +2510,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2534,7 +2534,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2587,22 +2587,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2664,22 +2664,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2694,7 +2694,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2741,28 +2741,28 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2782,76 +2782,76 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>6</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2880,10 +2880,10 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -2892,34 +2892,34 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -2936,7 +2936,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -2954,13 +2954,13 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -2969,43 +2969,43 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3061,92 +3061,92 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>67.86</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G2">
-        <v>28.57</v>
+        <v>13.79</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>78.56999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.79</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>79.31</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>20.69</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3157,39 +3157,39 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>82.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>17.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3198,30 +3198,30 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>10.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3258,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3283,306 +3283,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920110</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920110</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920120</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920391</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920391</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920127</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920128</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920128</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920128</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920152</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920152</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3624,146 +3324,146 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920128</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920152</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920391</v>
+        <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920120</v>
+        <v>21330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920122</v>
+        <v>21330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920127</v>
+        <v>21330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920134</v>
+        <v>21330051920117</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920111</v>
+        <v>21330051920118</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3771,16 +3471,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920112</v>
+        <v>21330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3788,16 +3488,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920113</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3805,16 +3505,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920114</v>
+        <v>21330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3822,16 +3522,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3839,16 +3539,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920116</v>
+        <v>21330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3856,16 +3556,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920117</v>
+        <v>21330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3873,16 +3573,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920118</v>
+        <v>21330051920124</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3890,13 +3590,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920119</v>
+        <v>21330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>121</v>
@@ -3907,13 +3607,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920121</v>
+        <v>21330051920126</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
         <v>122</v>
@@ -3924,13 +3624,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920123</v>
+        <v>21330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>123</v>
@@ -3941,13 +3641,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920124</v>
+        <v>20330051920275</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>124</v>
@@ -3958,13 +3658,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920125</v>
+        <v>21330051920128</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>125</v>
@@ -3975,13 +3675,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920126</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
+        <v>21330051920129</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
         <v>126</v>
@@ -3992,13 +3689,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920275</v>
+        <v>21330051920130</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
         <v>127</v>
@@ -4009,10 +3706,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920129</v>
+        <v>21330051920131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
         <v>128</v>
@@ -4023,13 +3723,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920130</v>
+        <v>18330051920377</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
         <v>129</v>
@@ -4040,13 +3740,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920131</v>
+        <v>21330051920132</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
         <v>130</v>
@@ -4057,13 +3757,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>18330051920377</v>
+        <v>20330051920152</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>131</v>
@@ -4074,13 +3774,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920132</v>
+        <v>21330051920133</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>132</v>
@@ -4091,13 +3791,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920133</v>
+        <v>21330051920134</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>133</v>
@@ -4145,39 +3845,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920120</v>
+        <v>21330051920110</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920120</v>
+        <v>21330051920110</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4191,45 +3891,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920127</v>
+        <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920127</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4237,19 +3937,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920117</v>
+        <v>21330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>49</v>
@@ -4260,22 +3960,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920118</v>
+        <v>21330051920128</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4283,25 +3983,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920122</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4309,13 +4009,13 @@
         <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
